--- a/On-the-job and self-study.xlsx
+++ b/On-the-job and self-study.xlsx
@@ -1,42 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27528"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bppserviceslimited-my.sharepoint.com/personal/mikehoffman_bpp_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{7157AA59-4E4D-4E8E-8BE0-52E15756D2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C80B640-BF09-4308-8685-B66F68689850}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D280A91A-DE60-4575-A34A-558A7388C718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11760" xr2:uid="{87251D64-A23B-4DC4-BF2E-D68309477306}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{87251D64-A23B-4DC4-BF2E-D68309477306}"/>
   </bookViews>
   <sheets>
     <sheet name="Log" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>On-the-job and self-guided learning hours log.</t>
   </si>
@@ -114,15 +103,30 @@
   <si>
     <t>Approved short-course certs</t>
   </si>
+  <si>
+    <t>31.01.2025</t>
+  </si>
+  <si>
+    <t>06.02.2025</t>
+  </si>
+  <si>
+    <t>07.02.2025</t>
+  </si>
+  <si>
+    <t>11.02.2025</t>
+  </si>
+  <si>
+    <t>Halyna Maslak</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,7 +345,7 @@
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -372,7 +376,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="8" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -726,7 +730,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF7142F-37B8-4965-8FB1-4A87CBC72984}">
   <dimension ref="A1:H51"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -737,7 +741,7 @@
     <col min="7" max="7" width="24.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -751,8 +755,8 @@
       <c r="G1" s="19"/>
       <c r="H1" s="19"/>
     </row>
-    <row r="2" spans="1:8" hidden="1"/>
-    <row r="3" spans="1:8" ht="77.45" customHeight="1">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:8" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -764,7 +768,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="22"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>3</v>
       </c>
@@ -773,11 +777,13 @@
       <c r="E4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="23" t="s">
+        <v>22</v>
+      </c>
       <c r="G4" s="23"/>
       <c r="H4" s="23"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>5</v>
       </c>
@@ -790,7 +796,7 @@
       <c r="G5" s="23"/>
       <c r="H5" s="23"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="14"/>
       <c r="B6" s="17" t="s">
         <v>7</v>
@@ -798,7 +804,7 @@
       <c r="C6" s="17"/>
       <c r="D6" s="15">
         <f>SUM(B9:E51)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="17" t="s">
@@ -807,10 +813,10 @@
       <c r="G6" s="17"/>
       <c r="H6" s="16">
         <f>SUM(F9:H51)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
         <v>9</v>
       </c>
@@ -823,7 +829,7 @@
       <c r="G7" s="21"/>
       <c r="H7" s="21"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -849,47 +855,67 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="5"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
+      <c r="D9" s="7">
+        <v>1</v>
+      </c>
       <c r="E9" s="7"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="10"/>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="5"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="D10" s="7">
+        <v>1</v>
+      </c>
       <c r="E10" s="7"/>
       <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="G10" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H10" s="10"/>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="5"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+      <c r="D11" s="7">
+        <v>1</v>
+      </c>
       <c r="E11" s="7"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10"/>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="5"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1</v>
+      </c>
       <c r="E12" s="7"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="10"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -899,7 +925,7 @@
       <c r="G13" s="9"/>
       <c r="H13" s="10"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -909,7 +935,7 @@
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -919,7 +945,7 @@
       <c r="G15" s="9"/>
       <c r="H15" s="10"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -929,7 +955,7 @@
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -939,7 +965,7 @@
       <c r="G17" s="9"/>
       <c r="H17" s="10"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -949,7 +975,7 @@
       <c r="G18" s="9"/>
       <c r="H18" s="10"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -959,7 +985,7 @@
       <c r="G19" s="9"/>
       <c r="H19" s="10"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -969,7 +995,7 @@
       <c r="G20" s="9"/>
       <c r="H20" s="10"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -979,7 +1005,7 @@
       <c r="G21" s="9"/>
       <c r="H21" s="10"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -989,7 +1015,7 @@
       <c r="G22" s="9"/>
       <c r="H22" s="10"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -999,7 +1025,7 @@
       <c r="G23" s="9"/>
       <c r="H23" s="10"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1009,7 +1035,7 @@
       <c r="G24" s="9"/>
       <c r="H24" s="10"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1019,7 +1045,7 @@
       <c r="G25" s="9"/>
       <c r="H25" s="10"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1029,7 +1055,7 @@
       <c r="G26" s="9"/>
       <c r="H26" s="10"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -1039,7 +1065,7 @@
       <c r="G27" s="9"/>
       <c r="H27" s="10"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -1049,7 +1075,7 @@
       <c r="G28" s="9"/>
       <c r="H28" s="10"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -1059,7 +1085,7 @@
       <c r="G29" s="9"/>
       <c r="H29" s="10"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -1069,7 +1095,7 @@
       <c r="G30" s="9"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -1079,7 +1105,7 @@
       <c r="G31" s="9"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -1089,7 +1115,7 @@
       <c r="G32" s="9"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -1099,7 +1125,7 @@
       <c r="G33" s="9"/>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -1109,7 +1135,7 @@
       <c r="G34" s="9"/>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -1119,7 +1145,7 @@
       <c r="G35" s="9"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -1129,7 +1155,7 @@
       <c r="G36" s="9"/>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -1139,7 +1165,7 @@
       <c r="G37" s="9"/>
       <c r="H37" s="10"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -1149,7 +1175,7 @@
       <c r="G38" s="9"/>
       <c r="H38" s="10"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -1159,7 +1185,7 @@
       <c r="G39" s="9"/>
       <c r="H39" s="10"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -1169,7 +1195,7 @@
       <c r="G40" s="9"/>
       <c r="H40" s="10"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -1179,7 +1205,7 @@
       <c r="G41" s="9"/>
       <c r="H41" s="10"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -1189,7 +1215,7 @@
       <c r="G42" s="9"/>
       <c r="H42" s="10"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -1199,7 +1225,7 @@
       <c r="G43" s="9"/>
       <c r="H43" s="10"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -1209,7 +1235,7 @@
       <c r="G44" s="9"/>
       <c r="H44" s="10"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -1219,7 +1245,7 @@
       <c r="G45" s="9"/>
       <c r="H45" s="10"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -1229,7 +1255,7 @@
       <c r="G46" s="9"/>
       <c r="H46" s="10"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -1239,7 +1265,7 @@
       <c r="G47" s="9"/>
       <c r="H47" s="10"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -1249,7 +1275,7 @@
       <c r="G48" s="9"/>
       <c r="H48" s="10"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -1259,7 +1285,7 @@
       <c r="G49" s="9"/>
       <c r="H49" s="10"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -1269,7 +1295,7 @@
       <c r="G50" s="9"/>
       <c r="H50" s="10"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>

--- a/On-the-job and self-study.xlsx
+++ b/On-the-job and self-study.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D280A91A-DE60-4575-A34A-558A7388C718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545E5D1D-4F5E-43DD-83C7-79DB1014A7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{87251D64-A23B-4DC4-BF2E-D68309477306}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{87251D64-A23B-4DC4-BF2E-D68309477306}"/>
   </bookViews>
   <sheets>
     <sheet name="Log" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>On-the-job and self-guided learning hours log.</t>
   </si>
@@ -117,6 +117,30 @@
   </si>
   <si>
     <t>Halyna Maslak</t>
+  </si>
+  <si>
+    <t>17.02.2025</t>
+  </si>
+  <si>
+    <t>19.02.2025</t>
+  </si>
+  <si>
+    <t>20.02.2025</t>
+  </si>
+  <si>
+    <t>24.02.2025</t>
+  </si>
+  <si>
+    <t>25.02.2025</t>
+  </si>
+  <si>
+    <t>26.02.2025</t>
+  </si>
+  <si>
+    <t>03.03.2025</t>
+  </si>
+  <si>
+    <t>06.03.2025</t>
   </si>
 </sst>
 </file>
@@ -804,7 +828,7 @@
       <c r="C6" s="17"/>
       <c r="D6" s="15">
         <f>SUM(B9:E51)</f>
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="17" t="s">
@@ -916,8 +940,12 @@
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="7">
+        <v>1</v>
+      </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -926,18 +954,26 @@
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
+      <c r="A14" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="E14" s="7">
+        <v>1</v>
+      </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="7">
+        <v>1</v>
+      </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -946,9 +982,15 @@
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
+      <c r="A16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1</v>
+      </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="9"/>
@@ -956,9 +998,13 @@
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
+      <c r="A17" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
+      <c r="C17" s="7">
+        <v>2</v>
+      </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="9"/>
@@ -966,9 +1012,13 @@
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
+      <c r="A18" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
+      <c r="C18" s="7">
+        <v>1</v>
+      </c>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="9"/>
@@ -976,8 +1026,12 @@
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="7"/>
+      <c r="A19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="7">
+        <v>1</v>
+      </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -986,10 +1040,16 @@
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="7">
+        <v>1</v>
+      </c>
       <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="D20" s="7">
+        <v>1</v>
+      </c>
       <c r="E20" s="7"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>

--- a/On-the-job and self-study.xlsx
+++ b/On-the-job and self-study.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545E5D1D-4F5E-43DD-83C7-79DB1014A7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FD765B-1848-4AB2-904F-9CE8FEF7996F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{87251D64-A23B-4DC4-BF2E-D68309477306}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{87251D64-A23B-4DC4-BF2E-D68309477306}"/>
   </bookViews>
   <sheets>
     <sheet name="Log" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>On-the-job and self-guided learning hours log.</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>06.03.2025</t>
+  </si>
+  <si>
+    <t>10.03.2025</t>
   </si>
 </sst>
 </file>
@@ -828,7 +831,7 @@
       <c r="C6" s="17"/>
       <c r="D6" s="15">
         <f>SUM(B9:E51)</f>
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="17" t="s">
@@ -1056,9 +1059,13 @@
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
+      <c r="A21" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
+      <c r="C21" s="7">
+        <v>0.5</v>
+      </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="9"/>

--- a/On-the-job and self-study.xlsx
+++ b/On-the-job and self-study.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FD765B-1848-4AB2-904F-9CE8FEF7996F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36BDE21-78A7-4BFD-A0CD-7F4FC2016AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{87251D64-A23B-4DC4-BF2E-D68309477306}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{87251D64-A23B-4DC4-BF2E-D68309477306}"/>
   </bookViews>
   <sheets>
     <sheet name="Log" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>On-the-job and self-guided learning hours log.</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>10.03.2025</t>
+  </si>
+  <si>
+    <t>18.03.2025</t>
   </si>
 </sst>
 </file>
@@ -831,7 +834,7 @@
       <c r="C6" s="17"/>
       <c r="D6" s="15">
         <f>SUM(B9:E51)</f>
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="17" t="s">
@@ -1073,10 +1076,14 @@
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
+      <c r="A22" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="7">
+        <v>1</v>
+      </c>
       <c r="E22" s="7"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>

--- a/On-the-job and self-study.xlsx
+++ b/On-the-job and self-study.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36BDE21-78A7-4BFD-A0CD-7F4FC2016AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA125D7D-C124-4C05-80F3-BB9007838613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{87251D64-A23B-4DC4-BF2E-D68309477306}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>On-the-job and self-guided learning hours log.</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>18.03.2025</t>
+  </si>
+  <si>
+    <t>24.03.2025</t>
   </si>
 </sst>
 </file>
@@ -834,7 +837,7 @@
       <c r="C6" s="17"/>
       <c r="D6" s="15">
         <f>SUM(B9:E51)</f>
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="17" t="s">
@@ -1090,9 +1093,13 @@
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
+      <c r="A23" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
+      <c r="C23" s="7">
+        <v>1</v>
+      </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="9"/>
